--- a/output/pdf_financials_xlsx/BUX.xlsx
+++ b/output/pdf_financials_xlsx/BUX.xlsx
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.386196</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.39317</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.401274</v>
       </c>
     </row>
     <row r="101">
@@ -4370,7 +4370,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.013253</v>
       </c>
@@ -4397,7 +4401,11 @@
           <t>Depreciation of right-of-use of asset</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>0.372943</v>
       </c>
